--- a/data/trans_camb/P6902-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 33,78</t>
+          <t>-11,76; 30,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 25,68</t>
+          <t>-14,72; 28,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 32,42</t>
+          <t>-22,23; 29,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 40,08</t>
+          <t>-4,3; 41,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 22,24</t>
+          <t>-27,43; 20,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,04; 5,73</t>
+          <t>-47,32; 4,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 30,19</t>
+          <t>-2,21; 29,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 18,08</t>
+          <t>-13,62; 18,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 13,65</t>
+          <t>-25,26; 12,35</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 94,73</t>
+          <t>-19,3; 84,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 71,76</t>
+          <t>-24,9; 80,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 92,9</t>
+          <t>-40,43; 76,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 78,83</t>
+          <t>-5,12; 82,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 43,31</t>
+          <t>-35,29; 37,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,19; 10,69</t>
+          <t>-61,78; 9,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 65,05</t>
+          <t>-2,75; 65,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 38,45</t>
+          <t>-20,38; 38,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,28; 26,47</t>
+          <t>-41,18; 25,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 25,25</t>
+          <t>-13,46; 23,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 1,09</t>
+          <t>-31,36; 0,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 23,76</t>
+          <t>-17,65; 23,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 13,07</t>
+          <t>-36,38; 10,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 23,95</t>
+          <t>-18,7; 25,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 19,22</t>
+          <t>-24,86; 18,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 14,16</t>
+          <t>-15,49; 14,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 3,63</t>
+          <t>-22,79; 3,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 17,37</t>
+          <t>-13,28; 17,27</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 82,69</t>
+          <t>-27,26; 65,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,25; 3,49</t>
+          <t>-61,93; 2,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 69,66</t>
+          <t>-36,45; 69,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,23; 27,23</t>
+          <t>-53,27; 20,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 52,0</t>
+          <t>-26,53; 53,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 40,87</t>
+          <t>-35,31; 39,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 34,04</t>
+          <t>-28,37; 37,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,85; 8,77</t>
+          <t>-42,73; 8,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 40,74</t>
+          <t>-25,17; 42,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 9,72</t>
+          <t>-34,76; 11,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 0,24</t>
+          <t>-45,73; -0,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 26,84</t>
+          <t>-15,58; 26,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 59,74</t>
+          <t>3,37; 60,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 42,05</t>
+          <t>-16,9; 44,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,79; 61,82</t>
+          <t>24,57; 63,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 24,64</t>
+          <t>-13,35; 25,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 7,52</t>
+          <t>-27,61; 7,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 37,46</t>
+          <t>6,21; 37,05</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,76; 32,7</t>
+          <t>-69,86; 39,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,72; 15,39</t>
+          <t>-89,91; 6,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 96,76</t>
+          <t>-28,64; 96,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1011,13</t>
+          <t>-4,66; 1078,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,81; 572,88</t>
+          <t>-70,61; 594,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,97; 1309,61</t>
+          <t>52,9; 1277,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 99,04</t>
+          <t>-34,46; 107,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,99; 36,71</t>
+          <t>-72,01; 30,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,13; 170,98</t>
+          <t>13,98; 165,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 28,5</t>
+          <t>-11,15; 29,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,31; 50,29</t>
+          <t>10,47; 50,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,98; 52,25</t>
+          <t>8,03; 51,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 30,13</t>
+          <t>-24,19; 31,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 35,57</t>
+          <t>-23,08; 31,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-52,45; 24,91</t>
+          <t>-55,89; 25,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 23,97</t>
+          <t>-7,14; 24,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 36,52</t>
+          <t>5,46; 37,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 33,04</t>
+          <t>-26,9; 32,9</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 82,52</t>
+          <t>-21,18; 81,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,09; 146,99</t>
+          <t>19,83; 147,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,27; 155,96</t>
+          <t>16,94; 147,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 73,42</t>
+          <t>-34,34; 76,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 88,25</t>
+          <t>-32,06; 80,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,7; 49,84</t>
+          <t>-77,83; 50,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 60,44</t>
+          <t>-12,66; 60,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,51; 93,69</t>
+          <t>7,98; 93,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 71,43</t>
+          <t>-47,37; 72,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-47,62; 2,17</t>
+          <t>-47,97; -2,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 66,4</t>
+          <t>3,78; 64,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 52,71</t>
+          <t>-2,89; 53,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-46,58; 41,9</t>
+          <t>-50,4; 40,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,23</t>
+          <t>0,0; 71,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 47,9</t>
+          <t>-22,13; 50,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 17,08</t>
+          <t>-33,15; 17,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,37; 59,46</t>
+          <t>9,04; 59,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 45,23</t>
+          <t>3,92; 49,5</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,04</t>
+          <t>-100,0; 40,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,39; 513,09</t>
+          <t>4,62; 400,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 351,18</t>
+          <t>-10,55; 344,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-53,87; 109,75</t>
+          <t>-58,5; 88,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 247,63</t>
+          <t>0,0; 247,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 143,86</t>
+          <t>-23,75; 161,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-64,25; 66,23</t>
+          <t>-65,52; 72,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,99; 235,34</t>
+          <t>18,92; 242,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,0; 182,34</t>
+          <t>6,95; 199,65</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 29,51</t>
+          <t>-14,7; 27,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 9,87</t>
+          <t>-38,94; 9,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 30,8</t>
+          <t>-15,34; 30,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 14,62</t>
+          <t>-54,0; 11,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-67,14; 22,35</t>
+          <t>-64,4; 19,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-46,38; 6,48</t>
+          <t>-46,91; 6,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 17,68</t>
+          <t>-19,09; 17,56</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-37,73; 5,4</t>
+          <t>-39,2; 3,96</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 18,68</t>
+          <t>-14,69; 19,93</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 106,83</t>
+          <t>-28,9; 90,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-74,57; 33,73</t>
+          <t>-76,05; 33,13</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 98,13</t>
+          <t>-28,2; 99,53</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-66,45; 22,79</t>
+          <t>-63,8; 18,49</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-82,45; 42,84</t>
+          <t>-81,83; 33,99</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,29; 12,47</t>
+          <t>-52,08; 11,52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 46,16</t>
+          <t>-32,81; 43,69</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-67,28; 13,01</t>
+          <t>-69,45; 11,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 45,45</t>
+          <t>-24,41; 54,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 29,93</t>
+          <t>-4,16; 29,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 9,8</t>
+          <t>-22,78; 10,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,88; 36,41</t>
+          <t>3,4; 35,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 29,37</t>
+          <t>-13,68; 29,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 40,38</t>
+          <t>-2,58; 37,4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,28; 43,65</t>
+          <t>9,26; 44,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 23,15</t>
+          <t>-2,35; 24,05</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 15,63</t>
+          <t>-8,35; 16,72</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,32; 34,18</t>
+          <t>12,78; 34,83</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 72,94</t>
+          <t>-8,81; 72,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-43,29; 24,57</t>
+          <t>-41,92; 26,08</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7,4; 98,34</t>
+          <t>6,52; 91,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 79,31</t>
+          <t>-22,67; 81,04</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 116,43</t>
+          <t>-1,63; 104,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,36; 128,66</t>
+          <t>14,55; 126,79</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 56,11</t>
+          <t>-4,83; 59,86</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 37,11</t>
+          <t>-16,39; 40,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>23,08; 85,33</t>
+          <t>22,31; 86,99</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 9,41</t>
+          <t>-23,12; 10,02</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 29,22</t>
+          <t>-7,21; 29,77</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>21,87; 52,21</t>
+          <t>23,55; 52,21</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 23,85</t>
+          <t>-25,0; 24,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 29,5</t>
+          <t>-21,98; 30,32</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,53; 48,07</t>
+          <t>1,9; 48,36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 10,58</t>
+          <t>-18,95; 10,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 23,71</t>
+          <t>-7,35; 23,02</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19,86; 46,31</t>
+          <t>19,82; 45,3</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 29,2</t>
+          <t>-51,76; 28,86</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 80,8</t>
+          <t>-15,13; 82,24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>47,36; 157,71</t>
+          <t>51,21; 157,79</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-46,32; 72,11</t>
+          <t>-47,8; 70,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 97,2</t>
+          <t>-43,1; 89,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,98; 157,33</t>
+          <t>12,83; 155,38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 29,58</t>
+          <t>-42,03; 28,22</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 65,21</t>
+          <t>-16,52; 64,47</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>45,01; 134,67</t>
+          <t>46,29; 130,06</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 10,75</t>
+          <t>-3,74; 10,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 6,81</t>
+          <t>-7,96; 6,68</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11,83; 25,95</t>
+          <t>11,14; 25,33</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 15,3</t>
+          <t>-3,92; 16,13</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 18,09</t>
+          <t>-0,21; 19,33</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 19,12</t>
+          <t>-9,75; 18,62</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 10,81</t>
+          <t>-0,8; 11,08</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 9,6</t>
+          <t>-1,51; 9,97</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,85; 21,39</t>
+          <t>5,18; 21,17</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 25,81</t>
+          <t>-8,34; 25,52</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 16,88</t>
+          <t>-17,57; 16,45</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>25,51; 64,31</t>
+          <t>23,74; 63,93</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 33,11</t>
+          <t>-6,75; 34,81</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 39,78</t>
+          <t>-0,39; 41,95</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 40,44</t>
+          <t>-17,14; 38,56</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 25,55</t>
+          <t>-1,52; 25,82</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 22,4</t>
+          <t>-3,23; 22,95</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>11,16; 49,41</t>
+          <t>11,51; 48,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6902-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>-8,98</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-22,39</t>
+          <t>-25,55</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,16</t>
+          <t>-15,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 30,74</t>
+          <t>-14,75; 30,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 28,29</t>
+          <t>-13,45; 25,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 29,8</t>
+          <t>-35,23; 15,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 41,25</t>
+          <t>-3,93; 38,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 20,1</t>
+          <t>-26,26; 19,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,32; 4,31</t>
+          <t>-50,78; -1,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 29,77</t>
+          <t>-2,99; 29,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 18,07</t>
+          <t>-13,33; 18,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 12,35</t>
+          <t>-33,16; 2,62</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>-18,18%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-33,39%</t>
+          <t>-38,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,9%</t>
+          <t>-27,69%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 84,6</t>
+          <t>-24,5; 84,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 80,29</t>
+          <t>-21,21; 73,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 76,89</t>
+          <t>-60,01; 44,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 82,13</t>
+          <t>-4,96; 78,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 37,71</t>
+          <t>-33,22; 37,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,78; 9,74</t>
+          <t>-65,71; -1,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 65,21</t>
+          <t>-5,06; 64,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 38,12</t>
+          <t>-20,65; 40,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 25,04</t>
+          <t>-52,6; 5,51</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,29</t>
+          <t>-5,1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>1,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 23,19</t>
+          <t>-12,01; 23,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,36; 0,61</t>
+          <t>-32,85; 0,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 23,97</t>
+          <t>-19,36; 25,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-36,38; 10,4</t>
+          <t>-38,74; 11,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 25,08</t>
+          <t>-19,64; 23,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 18,23</t>
+          <t>-25,77; 16,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 14,93</t>
+          <t>-14,34; 15,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 3,57</t>
+          <t>-22,54; 5,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 17,27</t>
+          <t>-13,22; 18,18</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,13%</t>
+          <t>-8,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 65,6</t>
+          <t>-22,98; 70,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,93; 2,04</t>
+          <t>-62,19; 3,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 69,07</t>
+          <t>-39,41; 74,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 20,06</t>
+          <t>-54,98; 22,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 53,68</t>
+          <t>-27,78; 48,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 39,83</t>
+          <t>-35,51; 36,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 37,36</t>
+          <t>-26,63; 38,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 8,38</t>
+          <t>-40,83; 14,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 42,89</t>
+          <t>-23,87; 46,41</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,03</t>
+          <t>45,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22,45</t>
+          <t>22,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 11,65</t>
+          <t>-38,66; 10,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-45,73; -0,73</t>
+          <t>-47,88; -2,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 26,94</t>
+          <t>-16,59; 26,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 60,77</t>
+          <t>0,93; 61,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 44,5</t>
+          <t>-14,99; 44,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,57; 63,12</t>
+          <t>21,33; 61,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 25,98</t>
+          <t>-12,65; 25,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,61; 7,21</t>
+          <t>-29,24; 7,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 37,05</t>
+          <t>5,81; 35,89</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>256,24%</t>
+          <t>258,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,35%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 39,92</t>
+          <t>-70,08; 39,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,91; 6,65</t>
+          <t>-89,7; 7,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 96,58</t>
+          <t>-31,05; 91,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 1078,35</t>
+          <t>-6,23; 1118,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,61; 594,8</t>
+          <t>-69,48; 761,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,9; 1277,4</t>
+          <t>47,84; 1129,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 107,25</t>
+          <t>-32,55; 105,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,01; 30,08</t>
+          <t>-72,22; 35,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 165,1</t>
+          <t>11,69; 164,82</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32,04</t>
+          <t>36,52</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-12,42</t>
+          <t>18,06</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>29,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 29,39</t>
+          <t>-13,11; 27,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,47; 50,38</t>
+          <t>8,07; 50,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,03; 51,15</t>
+          <t>13,67; 54,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 31,82</t>
+          <t>-25,1; 30,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 31,68</t>
+          <t>-23,13; 31,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-55,89; 25,75</t>
+          <t>-4,35; 43,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 24,39</t>
+          <t>-9,12; 24,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 37,37</t>
+          <t>4,54; 37,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-26,9; 32,9</t>
+          <t>14,97; 43,8</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-21,69%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>61,07%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 81,6</t>
+          <t>-25,37; 77,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,83; 147,27</t>
+          <t>16,31; 143,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,94; 147,27</t>
+          <t>25,17; 160,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 76,33</t>
+          <t>-35,26; 71,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 80,94</t>
+          <t>-30,58; 75,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 50,24</t>
+          <t>-5,62; 128,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 60,58</t>
+          <t>-15,51; 62,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,98; 93,8</t>
+          <t>7,9; 91,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 72,63</t>
+          <t>24,55; 110,4</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26,96</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25,58</t>
+          <t>22,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-47,97; -2,65</t>
+          <t>-45,09; -1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,78; 64,68</t>
+          <t>-2,93; 64,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 53,53</t>
+          <t>-2,42; 51,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 40,04</t>
+          <t>-48,5; 43,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,19</t>
+          <t>0,0; 71,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 50,93</t>
+          <t>-27,33; 45,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 17,51</t>
+          <t>-31,63; 17,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,04; 59,68</t>
+          <t>3,98; 59,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 49,5</t>
+          <t>-0,57; 44,36</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,62; 400,69</t>
+          <t>-6,06; 420,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 344,1</t>
+          <t>-6,34; 375,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 88,02</t>
+          <t>-55,46; 111,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 247,13</t>
+          <t>0,0; 250,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 161,03</t>
+          <t>-29,2; 149,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-65,52; 72,34</t>
+          <t>-66,34; 63,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18,92; 242,2</t>
+          <t>7,0; 228,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,95; 199,65</t>
+          <t>-1,24; 183,86</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9,69</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-21,21</t>
+          <t>-22,03</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 27,98</t>
+          <t>-15,53; 29,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 9,68</t>
+          <t>-37,16; 12,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 30,28</t>
+          <t>-17,1; 28,31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-54,0; 11,81</t>
+          <t>-54,84; 16,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 19,45</t>
+          <t>-65,39; 19,54</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 6,64</t>
+          <t>-46,64; 7,03</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 17,56</t>
+          <t>-20,09; 17,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 3,96</t>
+          <t>-37,5; 6,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 19,93</t>
+          <t>-18,44; 14,05</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-29,05%</t>
+          <t>-30,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>-0,68%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 90,67</t>
+          <t>-28,07; 103,48</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,05; 33,13</t>
+          <t>-72,7; 37,68</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 99,53</t>
+          <t>-30,65; 97,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 18,49</t>
+          <t>-65,78; 31,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-81,83; 33,99</t>
+          <t>-81,68; 32,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,08; 11,52</t>
+          <t>-53,69; 12,34</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 43,69</t>
+          <t>-33,03; 43,68</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-69,45; 11,89</t>
+          <t>-68,98; 18,42</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 54,16</t>
+          <t>-29,69; 35,9</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20,11</t>
+          <t>17,27</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,89</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23,57</t>
+          <t>21,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 29,38</t>
+          <t>-5,03; 28,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 10,59</t>
+          <t>-21,67; 10,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,4; 35,57</t>
+          <t>-0,11; 32,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 29,78</t>
+          <t>-14,08; 27,72</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 37,4</t>
+          <t>-0,87; 38,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,26; 44,67</t>
+          <t>9,43; 43,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 24,05</t>
+          <t>-2,93; 23,44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 16,72</t>
+          <t>-8,03; 17,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,78; 34,83</t>
+          <t>10,7; 33,43</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 72,29</t>
+          <t>-9,16; 72,25</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 26,08</t>
+          <t>-41,25; 26,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6,52; 91,98</t>
+          <t>0,3; 87,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,67; 81,04</t>
+          <t>-24,91; 75,23</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 104,89</t>
+          <t>-1,58; 105,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,55; 126,79</t>
+          <t>15,94; 126,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 59,86</t>
+          <t>-5,21; 56,76</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 40,62</t>
+          <t>-15,49; 41,61</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>22,31; 86,99</t>
+          <t>19,85; 83,58</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38,64</t>
+          <t>39,38</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,27</t>
+          <t>35,85</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>34,83</t>
+          <t>38,0</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 10,02</t>
+          <t>-23,32; 10,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 29,77</t>
+          <t>-7,6; 28,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>23,55; 52,21</t>
+          <t>24,07; 51,87</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 24,01</t>
+          <t>-23,87; 25,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 30,32</t>
+          <t>-23,91; 29,9</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,9; 48,36</t>
+          <t>18,88; 52,33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 10,21</t>
+          <t>-17,4; 9,55</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 23,02</t>
+          <t>-7,38; 23,17</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19,82; 45,3</t>
+          <t>26,87; 47,73</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-51,76; 28,86</t>
+          <t>-52,58; 28,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 82,24</t>
+          <t>-16,62; 81,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>51,21; 157,79</t>
+          <t>51,8; 156,95</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 70,38</t>
+          <t>-48,14; 76,35</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 89,9</t>
+          <t>-49,06; 93,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,83; 155,38</t>
+          <t>35,62; 177,09</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-42,03; 28,22</t>
+          <t>-37,53; 26,98</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 64,47</t>
+          <t>-16,94; 60,11</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>46,29; 130,06</t>
+          <t>57,38; 138,04</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18,43</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>16,05</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>15,22</t>
+          <t>18,41</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 10,52</t>
+          <t>-3,76; 10,4</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 6,68</t>
+          <t>-7,6; 7,24</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11,14; 25,33</t>
+          <t>10,54; 24,81</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 16,13</t>
+          <t>-4,02; 15,87</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 19,33</t>
+          <t>-0,47; 18,05</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 18,62</t>
+          <t>7,91; 23,63</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 11,08</t>
+          <t>-0,27; 10,73</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 9,97</t>
+          <t>-2,02; 10,16</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,18; 21,17</t>
+          <t>13,33; 23,63</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 25,52</t>
+          <t>-8,31; 25,86</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 16,45</t>
+          <t>-16,43; 17,69</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>23,74; 63,93</t>
+          <t>21,72; 61,13</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 34,81</t>
+          <t>-7,05; 34,04</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 41,95</t>
+          <t>-0,81; 40,37</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 38,56</t>
+          <t>13,97; 51,77</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 25,82</t>
+          <t>-0,8; 25,35</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 22,95</t>
+          <t>-4,13; 23,7</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>11,51; 48,91</t>
+          <t>26,93; 54,31</t>
         </is>
       </c>
     </row>
